--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>0.987779948109862</v>
       </c>
       <c r="E18" t="n">
-        <v>0.425</v>
+        <v>0.384</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>0.987779948109862</v>
       </c>
       <c r="E18" t="n">
-        <v>0.384</v>
+        <v>0.403</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>0.987779948109862</v>
       </c>
       <c r="E18" t="n">
-        <v>0.403</v>
+        <v>0.402</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>0.987779948109862</v>
       </c>
       <c r="E18" t="n">
-        <v>0.402</v>
+        <v>0.425</v>
       </c>
     </row>
     <row r="19">

--- a/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
+++ b/Figures/Chapter 1 - Soil Disturbance Seasonality/pairwise_adonis_22_same_sheet.xlsx
@@ -546,7 +546,7 @@
         <v>0.987779948109862</v>
       </c>
       <c r="E18" t="n">
-        <v>0.425</v>
+        <v>0.404</v>
       </c>
     </row>
     <row r="19">
